--- a/bench/corpus/clean-03.xlsx
+++ b/bench/corpus/clean-03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nyank\Desktop\後藤さんのclaude\ai-builders-2026\gridlint\bench\corpus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EC6F598-C66C-4205-A0DE-EA66E4EEFA3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F568A6A9-D132-4281-8E6F-04D13A1D0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2D0549D1-F949-4889-ADD6-4D7AD1C52065}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B7EFD2B0-B1C2-4B52-8687-45C93F298BDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Model" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Plan</t>
   </si>
@@ -56,43 +56,40 @@
     <t>Mar</t>
   </si>
   <si>
-    <t>Apr</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>Jun</t>
-  </si>
-  <si>
     <t>REVENUE</t>
   </si>
   <si>
+    <t>Content</t>
+  </si>
+  <si>
+    <t>Cloud hosting</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
     <t>Insurance</t>
   </si>
   <si>
+    <t>Total revenue</t>
+  </si>
+  <si>
+    <t>COST OF SALES</t>
+  </si>
+  <si>
     <t>Events</t>
   </si>
   <si>
-    <t>Sponsorships</t>
-  </si>
-  <si>
-    <t>Software tools</t>
-  </si>
-  <si>
-    <t>Total revenue</t>
-  </si>
-  <si>
-    <t>COST OF SALES</t>
+    <t>Agency fees</t>
+  </si>
+  <si>
+    <t>Salaries</t>
+  </si>
+  <si>
+    <t>Travel</t>
   </si>
   <si>
     <t>Subscriptions</t>
-  </si>
-  <si>
-    <t>Benefits</t>
-  </si>
-  <si>
-    <t>Services</t>
   </si>
   <si>
     <t>Total cost of sales</t>
@@ -494,21 +491,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7762F6-0DEE-47EF-BCB8-50E583C07494}">
-  <dimension ref="A1:H18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3534F73C-D5C4-4114-B29C-C92ACE59B5A8}">
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.625" customWidth="1"/>
-    <col min="3" max="4" width="10.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -521,337 +518,246 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="G3" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
       <c r="B5" s="1">
-        <v>-0.02</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="C5" s="2">
-        <v>141000</v>
+        <v>310000</v>
       </c>
       <c r="D5" s="2">
         <f>C5*(1+$B$5)</f>
-        <v>138180</v>
+        <v>333870</v>
       </c>
       <c r="E5" s="2">
         <f>D5*(1+$B$5)</f>
-        <v>135416.4</v>
-      </c>
-      <c r="F5" s="2">
-        <f>E5*(1+$B$5)</f>
-        <v>132708.07199999999</v>
-      </c>
-      <c r="G5" s="2">
-        <f>F5*(1+$B$5)</f>
-        <v>130053.91055999999</v>
-      </c>
-      <c r="H5" s="2">
-        <f>G5*(1+$B$5)</f>
-        <v>127452.83234879999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+        <v>359577.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1">
-        <v>-1.6E-2</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="C6" s="2">
-        <v>346000</v>
+        <v>96000</v>
       </c>
       <c r="D6" s="2">
         <f>C6*(1+$B$6)</f>
-        <v>340464</v>
+        <v>101664</v>
       </c>
       <c r="E6" s="2">
         <f>D6*(1+$B$6)</f>
-        <v>335016.576</v>
-      </c>
-      <c r="F6" s="2">
-        <f>E6*(1+$B$6)</f>
-        <v>329656.31078399997</v>
-      </c>
-      <c r="G6" s="2">
-        <f>F6*(1+$B$6)</f>
-        <v>324381.80981145595</v>
-      </c>
-      <c r="H6" s="2">
-        <f>G6*(1+$B$6)</f>
-        <v>319191.70085447264</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+        <v>107662.17599999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
-        <v>8.0000000000000002E-3</v>
+        <v>-0.02</v>
       </c>
       <c r="C7" s="2">
-        <v>206000</v>
+        <v>141000</v>
       </c>
       <c r="D7" s="2">
         <f>C7*(1+$B$7)</f>
-        <v>207648</v>
+        <v>138180</v>
       </c>
       <c r="E7" s="2">
         <f>D7*(1+$B$7)</f>
-        <v>209309.18400000001</v>
-      </c>
-      <c r="F7" s="2">
-        <f>E7*(1+$B$7)</f>
-        <v>210983.65747200002</v>
-      </c>
-      <c r="G7" s="2">
-        <f>F7*(1+$B$7)</f>
-        <v>212671.52673177602</v>
-      </c>
-      <c r="H7" s="2">
-        <f>G7*(1+$B$7)</f>
-        <v>214372.89894563024</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+        <v>135416.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1">
-        <v>7.4999999999999997E-2</v>
+        <v>-1.6E-2</v>
       </c>
       <c r="C8" s="2">
-        <v>287000</v>
+        <v>346000</v>
       </c>
       <c r="D8" s="2">
         <f>C8*(1+$B$8)</f>
-        <v>308525</v>
+        <v>340464</v>
       </c>
       <c r="E8" s="2">
         <f>D8*(1+$B$8)</f>
-        <v>331664.375</v>
-      </c>
-      <c r="F8" s="2">
-        <f>E8*(1+$B$8)</f>
-        <v>356539.203125</v>
-      </c>
-      <c r="G8" s="2">
-        <f>F8*(1+$B$8)</f>
-        <v>383279.64335937501</v>
-      </c>
-      <c r="H8" s="2">
-        <f>G8*(1+$B$8)</f>
-        <v>412025.61661132809</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+        <v>335016.576</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2">
         <f>SUM(C5:C8)</f>
-        <v>980000</v>
+        <v>893000</v>
       </c>
       <c r="D9" s="2">
         <f>SUM(D5:D8)</f>
-        <v>994817</v>
+        <v>914178</v>
       </c>
       <c r="E9" s="2">
         <f>SUM(E5:E8)</f>
-        <v>1011406.535</v>
-      </c>
-      <c r="F9" s="2">
-        <f>SUM(F5:F8)</f>
-        <v>1029887.243381</v>
-      </c>
-      <c r="G9" s="2">
-        <f>SUM(G5:G8)</f>
-        <v>1050386.8904626069</v>
-      </c>
-      <c r="H9" s="2">
-        <f>SUM(H5:H8)</f>
-        <v>1073043.0487602311</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+        <v>937673.14199999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>0.06</v>
+        <v>5.8000000000000003E-2</v>
       </c>
       <c r="C11" s="2">
-        <v>46000</v>
+        <v>206000</v>
       </c>
       <c r="D11" s="2">
         <f>C11*(1+$B$11)</f>
-        <v>48760</v>
+        <v>217948</v>
       </c>
       <c r="E11" s="2">
         <f>D11*(1+$B$11)</f>
-        <v>51685.600000000006</v>
-      </c>
-      <c r="F11" s="2">
-        <f>E11*(1+$B$11)</f>
-        <v>54786.736000000012</v>
-      </c>
-      <c r="G11" s="2">
-        <f>F11*(1+$B$11)</f>
-        <v>58073.940160000013</v>
-      </c>
-      <c r="H11" s="2">
-        <f>G11*(1+$B$11)</f>
-        <v>61558.376569600019</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+        <v>230588.984</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1">
-        <v>-1.9E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C12" s="2">
-        <v>378000</v>
+        <v>287000</v>
       </c>
       <c r="D12" s="2">
         <f>C12*(1+$B$12)</f>
-        <v>370818</v>
+        <v>308525</v>
       </c>
       <c r="E12" s="2">
         <f>D12*(1+$B$12)</f>
-        <v>363772.45799999998</v>
-      </c>
-      <c r="F12" s="2">
-        <f>E12*(1+$B$12)</f>
-        <v>356860.78129799996</v>
-      </c>
-      <c r="G12" s="2">
-        <f>F12*(1+$B$12)</f>
-        <v>350080.42645333795</v>
-      </c>
-      <c r="H12" s="2">
-        <f>G12*(1+$B$12)</f>
-        <v>343428.89835072454</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+        <v>331664.375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="1">
-        <v>8.2000000000000003E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="C13" s="2">
-        <v>54000</v>
+        <v>55000</v>
       </c>
       <c r="D13" s="2">
         <f>C13*(1+$B$13)</f>
-        <v>58428.000000000007</v>
+        <v>57474.999999999993</v>
       </c>
       <c r="E13" s="2">
         <f>D13*(1+$B$13)</f>
-        <v>63219.096000000012</v>
-      </c>
-      <c r="F13" s="2">
-        <f>E13*(1+$B$13)</f>
-        <v>68403.06187200002</v>
-      </c>
-      <c r="G13" s="2">
-        <f>F13*(1+$B$13)</f>
-        <v>74012.112945504021</v>
-      </c>
-      <c r="H13" s="2">
-        <f>G13*(1+$B$13)</f>
-        <v>80081.106207035351</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+        <v>60061.374999999985</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="C14" s="2">
+        <v>46000</v>
+      </c>
+      <c r="D14" s="2">
+        <f>C14*(1+$B$14)</f>
+        <v>48760</v>
+      </c>
+      <c r="E14" s="2">
+        <f>D14*(1+$B$14)</f>
+        <v>51685.600000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>378000</v>
+      </c>
+      <c r="D15" s="2">
+        <f>C15*(1+$B$15)</f>
+        <v>370818</v>
+      </c>
+      <c r="E15" s="2">
+        <f>D15*(1+$B$15)</f>
+        <v>363772.45799999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2">
+        <f>SUM(C11:C15)</f>
+        <v>972000</v>
+      </c>
+      <c r="D16" s="2">
+        <f>SUM(D11:D15)</f>
+        <v>1003526</v>
+      </c>
+      <c r="E16" s="2">
+        <f>SUM(E11:E15)</f>
+        <v>1037772.7919999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2">
-        <f>SUM(C11:C13)</f>
-        <v>478000</v>
-      </c>
-      <c r="D14" s="2">
-        <f>SUM(D11:D13)</f>
-        <v>478006</v>
-      </c>
-      <c r="E14" s="2">
-        <f>SUM(E11:E13)</f>
-        <v>478677.15399999998</v>
-      </c>
-      <c r="F14" s="2">
-        <f>SUM(F11:F13)</f>
-        <v>480050.57917000004</v>
-      </c>
-      <c r="G14" s="2">
-        <f>SUM(G11:G13)</f>
-        <v>482166.47955884197</v>
-      </c>
-      <c r="H14" s="2">
-        <f>SUM(H11:H13)</f>
-        <v>485068.38112735993</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="C18" s="2">
+        <f>SUM(C9,C16)</f>
+        <v>1865000</v>
+      </c>
+      <c r="D18" s="2">
+        <f>SUM(D9,D16)</f>
+        <v>1917704</v>
+      </c>
+      <c r="E18" s="2">
+        <f>SUM(E9,E16)</f>
+        <v>1975445.9339999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="2">
-        <f>SUM(C9,C14)</f>
-        <v>1458000</v>
-      </c>
-      <c r="D16" s="2">
-        <f>SUM(D9,D14)</f>
-        <v>1472823</v>
-      </c>
-      <c r="E16" s="2">
-        <f>SUM(E9,E14)</f>
-        <v>1490083.689</v>
-      </c>
-      <c r="F16" s="2">
-        <f>SUM(F9,F14)</f>
-        <v>1509937.8225509999</v>
-      </c>
-      <c r="G16" s="2">
-        <f>SUM(G9,G14)</f>
-        <v>1532553.3700214489</v>
-      </c>
-      <c r="H16" s="2">
-        <f>SUM(H9,H14)</f>
-        <v>1558111.4298875909</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="2">
-        <f>SUM(C16:H16)</f>
-        <v>9021509.3114600405</v>
+      <c r="C20" s="2">
+        <f>SUM(C18:E18)</f>
+        <v>5758149.9340000004</v>
       </c>
     </row>
   </sheetData>
